--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 42157-2026 artfynd.xlsx
+++ b/artfynd/A 42157-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137283278</v>
       </c>
       <c r="B2" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
